--- a/data/evaluation/entity_accuracy.xlsx
+++ b/data/evaluation/entity_accuracy.xlsx
@@ -688,7 +688,7 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_004; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RETURN_002; RELOC_002; RELOC_005</t>
+          <t>CASE_001; RETURN_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RELOC_002; RELOC_005</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_001; RETURN_004; RELOC_006; RELOC_002</t>
+          <t>RELOC_005; RELOC_001; RELOC_006; RETURN_004; RELOC_002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; RELOC_005; RETURN_001; RELOC_001; RELOC_004; RETURN_004; RELOC_006; RELOC_002</t>
+          <t>CASE_003; CASE_002; DOC_001; RELOC_005; RETURN_001; RELOC_001; RELOC_004; RELOC_006; RETURN_004; RELOC_002</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004; RETURN_001; PLUS1_002; RELOC_007; RELOC_003</t>
+          <t>RETURN_001; RETURN_004; PLUS1_002; RELOC_007; RELOC_003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; RETURN_004; RETURN_001; CASE_010; RELOC_005; RELOC_001; PLUS1_002; RELOC_007; RELOC_003; WH_002</t>
+          <t>CASE_002; RETURN_001; RETURN_004; CASE_010; RELOC_005; RELOC_001; PLUS1_002; RELOC_007; RELOC_003; WH_002</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; TRD_003; RELOC_003; RELOC_006</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; TRD_003; RELOC_003; RELOC_006</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; RELOC_003; RELOC_005; WH_002; RETURN_004; RELOC_008; RELOC_002; RELOC_004; RELOC_001</t>
+          <t>TRD_003; CASE_010; RELOC_005; RELOC_003; WH_002; RETURN_004; RELOC_008; RELOC_002; RELOC_004; RELOC_001</t>
         </is>
       </c>
     </row>
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2009,16 +2009,16 @@
         <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; CSIS_001</t>
+          <t>DOC_001; CASE_003</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; CASE_010; RELOC_001; RELOC_005; CSIS_001</t>
+          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; CASE_010; RETURN_002; RELOC_001; RELOC_005</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RETURN_001; RETURN_004; RETURN_003; RELOC_006; RELOC_003; RELOC_004</t>
+          <t>RETURN_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; RELOC_003; RELOC_005; RETURN_004; RELOC_008; RELOC_002</t>
+          <t>TRD_003; RELOC_005; RELOC_003; RETURN_004; RELOC_008; RELOC_002</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; RETURN_001; RELOC_001; RELOC_005</t>
+          <t>TRD_003; CASE_002; RETURN_001; RETURN_002; RELOC_001; RELOC_005</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.927</v>
+        <v>0.929</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.854</v>
+        <v>0.858</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/entity_accuracy.xlsx
+++ b/data/evaluation/entity_accuracy.xlsx
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -575,16 +575,16 @@
         <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004; RELOC_003; RELOC_002; RELOC_001; PLUS1_003; CASE_005; CASE_004; CASE_001; CASE_006</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; TRD_003; CNGOV_001; UNCTAD_001</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; CASE_007; PLUS1_004; CASE_010; CASE_003; CASE_002; TRD_003; TRD_001; RELOC_005</t>
+          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; TRD_001; CASE_001; CASE_008; CASE_004; CASE_005</t>
         </is>
       </c>
     </row>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -683,12 +683,16 @@
         <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001; IMF_001</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RELOC_002; RELOC_005</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; CNGOV_001; UNCTAD_001; IMF_001</t>
         </is>
       </c>
     </row>
@@ -729,12 +733,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_004; RELOC_003; RELOC_006; RETURN_001; RETURN_004; RELOC_001; RELOC_008; RELOC_002; RELOC_007</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; CNGOV_001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_004; RELOC_003; RELOC_006; RETURN_001; RETURN_004; RELOC_001; RELOC_008; RELOC_002; RELOC_007</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; CNGOV_001</t>
         </is>
       </c>
     </row>
@@ -785,12 +789,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_001; RELOC_006; RETURN_004; RELOC_002</t>
+          <t>CASE_010; CASE_001; TRD_003; UNCTAD_001; MOFCOM_001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; RELOC_005; RETURN_001; RELOC_001; RELOC_004; RELOC_006; RETURN_004; RELOC_002</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001; CASE_008; CASE_007; TRD_003; UNCTAD_001; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -816,13 +820,13 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -837,12 +841,16 @@
         <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_001</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002; RELOC_006; RETURN_001; RELOC_004; RELOC_003; RELOC_005</t>
+          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002; CASE_002; CASE_003; CASE_001; CASE_010; TRD_001</t>
         </is>
       </c>
     </row>
@@ -898,7 +906,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001; CASE_002; CSIS_001; CASE_003; MOFCOM_002; TRD_001</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001; CASE_002; CSIS_001; CASE_003; TRD_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -924,13 +932,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -945,16 +953,16 @@
         <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; UNCTAD_001; RELOC_007</t>
+          <t>UNCTAD_001; CSIS_001; MOFCOM_001; WH_002</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001; RETURN_001; RELOC_005; UNCTAD_001; RELOC_007</t>
+          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001; UNCTAD_001; CSIS_001; MOFCOM_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1018,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; RETURN_001; RELOC_005; TRD_001</t>
+          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; TRD_003; CASE_003; TRD_001; TRD_002; CASE_007</t>
         </is>
       </c>
     </row>
@@ -1036,13 +1044,13 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1057,16 +1065,16 @@
         <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001; RETURN_004; PLUS1_002; RELOC_007; RELOC_003</t>
+          <t>MOFCOM_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; RETURN_001; RETURN_004; CASE_010; RELOC_005; RELOC_001; PLUS1_002; RELOC_007; RELOC_003; WH_002</t>
+          <t>CASE_002; CASE_010; TRD_003; WH_002; WH_001; CASE_001; CASE_009; MOFCOM_001; UNCTAD_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -1092,13 +1100,13 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1113,16 +1121,16 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001</t>
+          <t>IMF_001; UNCTAD_001; WEF_001; CASE_001; WTO_001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; RETURN_001; CNGOV_001; RETURN_004; RELOC_004; PLUS1_001; RELOC_006; RELOC_005; UNCTAD_001; PLUS1_002</t>
+          <t>IMF_001; CNGOV_001; UNCTAD_001; WEF_001; CASE_001; TRD_001; TRD_003; KPMG_001; CASE_002; WTO_001</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1171,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; CASE_004; CASE_001; MOFCOM_001; CASE_005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; CASE_004; CASE_001; MOFCOM_001; CASE_005</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1217,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; RETURN_004; IMF_001; RETURN_001; WTO_001; WEF_001; MCK_001; CNGOV_001; RELOC_007; RELOC_006</t>
+          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; RETURN_004; IMF_001; RETURN_001; WTO_001; WEF_001; MCK_001; CNGOV_001; RELOC_007; RELOC_006</t>
+          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1348,13 +1356,13 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1369,12 +1377,16 @@
         <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>WH_002; UNCTAD_001; CSIS_001</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_006; RELOC_003; RELOC_004; TRD_003; RETURN_001; RELOC_005; RELOC_001; WH_002; RELOC_008</t>
+          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_003; CASE_002; CASE_010; UNCTAD_001; CSIS_001; CASE_007</t>
         </is>
       </c>
     </row>
@@ -1400,13 +1412,13 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1421,12 +1433,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>WTO_001; CSIS_001; UNCTAD_001; IMF_001</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; RELOC_005; RELOC_003; WH_002; RETURN_004; RELOC_008; RELOC_002; RELOC_004; RELOC_001</t>
+          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; WH_001; UNCTAD_001; TRD_001; CASE_002; IMF_001</t>
         </is>
       </c>
     </row>
@@ -1452,13 +1468,13 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1473,12 +1489,16 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; MOFCOM_001; TRD_002; ITA_001</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_006; RELOC_004; RELOC_002; RETURN_001; RELOC_008; RELOC_007; RELOC_001; RELOC_003; PLUS1_002</t>
+          <t>TRD_003; CASE_002; CASE_008; TRD_001; CASE_001; MOFCOM_001; TRD_002; ITA_001; KPMG_001; CASE_007</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1539,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RETURN_001; RELOC_004; RELOC_001; PLUS1_001; RETURN_004; RELOC_003; RELOC_006; RELOC_002; RELOC_008</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003; CASE_007; CASE_006; CASE_005; CNGOV_001; MOFCOM_002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005; RETURN_001; RELOC_004; RELOC_001; PLUS1_001; RETURN_004; RELOC_003; RELOC_006; RELOC_002; RELOC_008</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003; CASE_007; CASE_006; CASE_005; CNGOV_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -1550,13 +1570,13 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1571,16 +1591,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; CSIS_001</t>
+          <t>WTO_001; CSIS_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; RETURN_001; WH_001; RETURN_004; WTO_001; TRD_001; CSIS_001; RELOC_006</t>
+          <t>TRD_003; WH_002; CASE_010; WH_001; WTO_001; TRD_001; CSIS_001; UNCTAD_001; TRD_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1651,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; RETURN_001</t>
+          <t>CSIS_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; TRD_003; RELOC_005; CASE_003; RETURN_001; RELOC_004</t>
+          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; TRD_003; CASE_003; TRD_001; UNCTAD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -1662,13 +1682,13 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1683,16 +1703,16 @@
         <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>MOFCOM_001; CASE_008</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; RETURN_001; RELOC_006; MOFCOM_001; CASE_003; RELOC_005; CASE_010; CASE_002</t>
+          <t>BIS_001; BIS_002; CASE_009; CASE_003; MOFCOM_001; CASE_010; CASE_001; CASE_002; MOFCOM_002; CASE_008</t>
         </is>
       </c>
     </row>
@@ -1718,13 +1738,13 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1739,16 +1759,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WH_002; CSIS_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; RELOC_005; CSIS_001; RELOC_002; RELOC_006; RELOC_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; CSIS_001; WH_001; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1794,13 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>0.6</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1795,16 +1815,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002; CSIS_001; RETURN_001; RELOC_006</t>
+          <t>CSIS_001; CASE_008</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; RELOC_005; RELOC_002; CSIS_001; RETURN_001; RELOC_006; RELOC_004; RELOC_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; TRD_003; CASE_008; CASE_003; TRD_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1865,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; PLUS1_002; CNGOV_001; RETURN_001; RETURN_004; PLUS1_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; PLUS1_002; CNGOV_001; RETURN_001; RETURN_004; PLUS1_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1921,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_001</t>
+          <t>WTO_001; MOFCOM_001</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001; CASE_001; RELOC_006; RETURN_001; MOFCOM_002; CASE_003; RELOC_004</t>
+          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001; MOFCOM_002; CASE_003; WTO_001; CASE_010; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1982,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; RELOC_005; TRD_003; WH_001; CSIS_001; RETURN_001</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1988,13 +2008,13 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2009,16 +2029,16 @@
         <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003</t>
+          <t>DOC_001; CASE_003; CSIS_001; WTO_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; CASE_010; RETURN_002; RELOC_001; RELOC_005</t>
+          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003; CASE_010; CSIS_001; WTO_001; WH_001; UNCTAD_001</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2079,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_001; UNCTAD_001; CNGOV_001; RETURN_001; PLUS1_001; RELOC_001; RELOC_005; RELOC_002; PLUS1_002</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001; TRD_003; CASE_008; CASE_004; CASE_006; CASE_005</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_001; UNCTAD_001; CNGOV_001; RETURN_001; PLUS1_001; RELOC_001; RELOC_005; RELOC_002; PLUS1_002</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001; TRD_003; CASE_008; CASE_004; CASE_006; CASE_005</t>
         </is>
       </c>
     </row>
@@ -2090,13 +2110,13 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2111,12 +2131,16 @@
         <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RETURN_001; RELOC_006; WH_001; RELOC_004; RELOC_005; RELOC_002; TRD_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; TRD_001; TRD_003; CASE_003; CSIS_001; CASE_002; TRD_002; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2222,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004; RELOC_003; RELOC_002; RELOC_001; PLUS1_003</t>
+          <t>CASE_005; CASE_004; CASE_006; CASE_008; CASE_007; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2250,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RELOC_006; RETURN_004; RELOC_003; RELOC_002; RELOC_001; PLUS1_003</t>
+          <t>CASE_005; CASE_004; CASE_006; TRD_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2278,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; CASE_007; PLUS1_004; CASE_002; TRD_003</t>
+          <t>CASE_007; CASE_002; TRD_003; TRD_001; CASE_008; CASE_004</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2306,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004; CASE_007; PLUS1_004; CASE_010; CASE_003</t>
+          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2338,7 +2362,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RELOC_004; PLUS1_004; CASE_010; CASE_003; CASE_002; TRD_001</t>
+          <t>CASE_010; CASE_003; CASE_002; TRD_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2390,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_004</t>
+          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2418,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RETURN_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003</t>
+          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2446,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_003; RELOC_006; RELOC_003; RELOC_004</t>
+          <t>CASE_001</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2474,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; RETURN_001; RELOC_004</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_008; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2502,11 +2526,11 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MOFCOM_001; MOFCOM_002; RELOC_006; RETURN_001; RELOC_004; RELOC_003</t>
+          <t>MOFCOM_002; CASE_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2558,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MOFCOM_002; RELOC_006; RETURN_001; RELOC_004; RELOC_003; RELOC_005</t>
+          <t>MOFCOM_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2586,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; MOFCOM_002; RELOC_004; RELOC_005</t>
+          <t>BIS_001; BIS_002; CASE_009; MOFCOM_002; CASE_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -2726,11 +2750,11 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_003; RETURN_001</t>
+          <t>CASE_010; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2754,11 +2778,11 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; TRD_003; TRD_001</t>
+          <t>CASE_010; CASE_002; TRD_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2810,11 +2834,11 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CASE_003; RELOC_005</t>
+          <t>CASE_010; WH_001; CASE_002; CASE_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2838,11 +2862,11 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; CASE_002; CASE_003; TRD_003; RELOC_005</t>
+          <t>CASE_010; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2866,11 +2890,11 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002</t>
+          <t>CASE_010; TRD_003; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2922,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; RELOC_005; RELOC_001; WH_002</t>
+          <t>CASE_002; CASE_010; WH_001; CASE_001; CASE_009; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2950,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RETURN_001; CNGOV_001; RETURN_004; RELOC_004; PLUS1_001; RELOC_006</t>
+          <t>CNGOV_001; TRD_001; TRD_003; KPMG_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2982,7 +3006,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>FR_001; WH_002</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3062,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_006; RELOC_003; RELOC_004; TRD_003; RETURN_001</t>
+          <t>TRD_001; TRD_003; CASE_002; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3062,11 +3086,11 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RELOC_006; RELOC_003; RELOC_004; RETURN_001; RELOC_005; RELOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3118,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_004; TRD_003; RETURN_001; WH_002</t>
+          <t>TRD_001; TRD_003; TRD_002; CASE_003; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3146,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_006; RELOC_003; TRD_003; RELOC_001; WH_002</t>
+          <t>TRD_001; TRD_003; TRD_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3174,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_004; RELOC_005; RELOC_001; WH_002</t>
+          <t>TRD_001; TRD_002; CASE_003; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3202,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRD_001; RELOC_003; TRD_003; RELOC_005; WH_002</t>
+          <t>TRD_001; TRD_003; TRD_002; CASE_003; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3230,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; RELOC_005; RELOC_003; RETURN_004; RELOC_008; RELOC_002</t>
+          <t>TRD_003; TRD_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3258,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3286,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RELOC_005; RELOC_006; RELOC_004; RELOC_002; RETURN_001; RELOC_008</t>
+          <t>TRD_003; CASE_002; CASE_008; TRD_001; KPMG_001; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3314,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; RETURN_001; TRD_001</t>
+          <t>TRD_003; CASE_010; TRD_001; TRD_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3342,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; RETURN_004; TRD_001; RELOC_006</t>
+          <t>TRD_003; CASE_010; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3398,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003</t>
+          <t>CASE_002; CASE_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3454,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; RELOC_005; CASE_003</t>
+          <t>CASE_010; WH_001; CASE_002; CASE_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3482,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; TRD_003; RELOC_005; CASE_003</t>
+          <t>CASE_010; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3482,11 +3506,11 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RETURN_001; RELOC_006; RELOC_005; CASE_002</t>
+          <t>CASE_002; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3538,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; CASE_003; RELOC_005; CASE_010</t>
+          <t>BIS_001; BIS_002; CASE_009; CASE_003; CASE_010; CASE_001</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3594,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003</t>
+          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3622,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; WH_002; CASE_010; RELOC_002; RELOC_006</t>
+          <t>DOC_001; CASE_002; CASE_010; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3650,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; RELOC_005</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3678,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; RELOC_005</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_010; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3706,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001</t>
+          <t>CASE_010; WH_002; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3734,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; RELOC_005; RELOC_004; RELOC_001</t>
+          <t>CASE_010; WH_001; CASE_002; CASE_003; TRD_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3818,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001; CASE_001; MOFCOM_002</t>
+          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3846,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; RETURN_001</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3874,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CASE_002; RELOC_005; TRD_003; RETURN_001</t>
+          <t>CASE_002; TRD_003; CASE_008; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3930,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; RELOC_005</t>
+          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3958,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; RETURN_001; RETURN_002; RELOC_001; RELOC_005</t>
+          <t>TRD_003; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3986,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010</t>
+          <t>TRD_003; WH_002; CASE_010; WH_001</t>
         </is>
       </c>
     </row>
@@ -3990,7 +4014,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RETURN_001; RELOC_004; TRD_001; TRD_003</t>
+          <t>CASE_010; TRD_001; TRD_003; CASE_003; CASE_002; TRD_002</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4042,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; RELOC_006; RELOC_002; TRD_001; TRD_003</t>
+          <t>CASE_010; TRD_001; TRD_003; CASE_002; TRD_002</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4098,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; RELOC_004; RELOC_005; TRD_001</t>
+          <t>CASE_010; WH_001; TRD_001; CASE_003; CASE_002; TRD_002</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4146,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.929</v>
+        <v>0.885</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -4152,7 +4176,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.858</v>
+        <v>0.771</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -4212,7 +4236,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/entity_accuracy.xlsx
+++ b/data/evaluation/entity_accuracy.xlsx
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -575,16 +575,16 @@
         <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; UNCTAD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; TRD_003; CNGOV_001; UNCTAD_001</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; TRD_003; CNGOV_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; CNGOV_001; UNCTAD_001; IMF_001</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; KPMG_001; CNGOV_001; EU_003; CASE_010</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; CNGOV_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_001; CASE_002; TRD_003; CNGOV_001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; CNGOV_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_001; CASE_002; TRD_003; CNGOV_001</t>
         </is>
       </c>
     </row>
@@ -764,13 +764,13 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -785,16 +785,16 @@
         <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_001; TRD_003; UNCTAD_001; MOFCOM_001</t>
+          <t>CASE_010; CASE_001; EU_003; MOFCOM_002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001; CASE_008; CASE_007; TRD_003; UNCTAD_001; MOFCOM_001</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001; CASE_008; CASE_007; EU_003; MOFCOM_002; CASE_004</t>
         </is>
       </c>
     </row>
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -841,16 +841,12 @@
         <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>MOFCOM_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002; CASE_002; CASE_003; CASE_001; CASE_010; TRD_001</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; IRS_001; EU_003; CASE_003; UST_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -906,7 +902,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001; CASE_002; CSIS_001; CASE_003; TRD_001; MOFCOM_002</t>
+          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; CASE_002; CSIS_001; CASE_003; IRS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -932,13 +928,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -953,16 +949,16 @@
         <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; CSIS_001; MOFCOM_001; WH_002</t>
+          <t>CSIS_001; EU_003</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001; UNCTAD_001; CSIS_001; MOFCOM_001; WH_002</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001; ITA_001; CSIS_001; CASE_010; UST_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1014,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; TRD_003; CASE_003; TRD_001; TRD_002; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; TRD_001; TRD_003; CASE_007; TRD_002</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1065,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MOFCOM_001; UNCTAD_001</t>
+          <t>CASE_008; EU_003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; TRD_003; WH_002; WH_001; CASE_001; CASE_009; MOFCOM_001; UNCTAD_001; MOFCOM_002</t>
+          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001; TRD_003; CASE_009; CASE_008; MOFCOM_002; EU_003</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1121,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WEF_001; CASE_001; WTO_001</t>
+          <t>IMF_001; UNCTAD_001; CASE_001; MCK_001; CSIS_001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; CNGOV_001; UNCTAD_001; WEF_001; CASE_001; TRD_001; TRD_003; KPMG_001; CASE_002; WTO_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001; IRS_001; CSIS_001; EU_003; UST_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1167,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; CASE_004; CASE_001; MOFCOM_001; CASE_005</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; CASE_005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; CASE_004; CASE_001; MOFCOM_001; CASE_005</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; CASE_005</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1213,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1274,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; MOFCOM_002; CASE_003; TRD_001; CASE_002</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; MOFCOM_002; CASE_003; IRS_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1326,7 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; CASE_002; CASE_003; MOFCOM_002; WH_002; WH_001</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; CASE_002; UST_001; MOFCOM_002; CASE_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -1356,13 +1352,13 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1377,16 +1373,16 @@
         <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>WH_002; UNCTAD_001; CSIS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_003; CASE_002; CASE_010; UNCTAD_001; CSIS_001; CASE_007</t>
+          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002; CASE_002; CASE_010; IRS_001; CSIS_001; CASE_007</t>
         </is>
       </c>
     </row>
@@ -1412,13 +1408,13 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0.6</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1433,16 +1429,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; CSIS_001; UNCTAD_001; IMF_001</t>
+          <t>CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; WH_001; UNCTAD_001; TRD_001; CASE_002; IMF_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WH_001; WTO_001; CASE_002; CASE_008; UST_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1468,13 +1464,13 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0.6</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1489,16 +1485,16 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; MOFCOM_001; TRD_002; ITA_001</t>
+          <t>CASE_001; TRD_002</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; TRD_001; CASE_001; MOFCOM_001; TRD_002; ITA_001; KPMG_001; CASE_007</t>
+          <t>CASE_002; TRD_003; CASE_008; CASE_001; TRD_001; IRS_001; EU_003; TRD_002; MOFCOM_002; CASE_007</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1535,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003; CASE_007; CASE_006; CASE_005; CNGOV_001; MOFCOM_002</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004; CASE_007; CASE_006; CASE_005; CNGOV_001; EU_004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_004; CASE_003; CASE_007; CASE_006; CASE_005; CNGOV_001; MOFCOM_002</t>
+          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004; CASE_007; CASE_006; CASE_005; CNGOV_001; EU_004</t>
         </is>
       </c>
     </row>
@@ -1570,13 +1566,13 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1591,16 +1587,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; CSIS_001; UNCTAD_001</t>
+          <t>CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; WH_001; WTO_001; TRD_001; CSIS_001; UNCTAD_001; TRD_002; CASE_003</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001; CSIS_001; TRD_001; WTO_001; TRD_002; CASE_003; CASE_002</t>
         </is>
       </c>
     </row>
@@ -1626,13 +1622,13 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1647,16 +1643,16 @@
         <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; UNCTAD_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; TRD_003; CASE_003; TRD_001; UNCTAD_001; TRD_002</t>
+          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; CASE_003; TRD_003; TRD_001; UST_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1678,13 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1703,16 +1699,12 @@
         <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>MOFCOM_001; CASE_008</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; CASE_003; MOFCOM_001; CASE_010; CASE_001; CASE_002; MOFCOM_002; CASE_008</t>
+          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001; CASE_003; CASE_010; UST_001; CASE_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1755,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CSIS_001</t>
+          <t>CSIS_001; EU_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; CSIS_001; WH_001; TRD_001; TRD_002; TRD_003</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; CSIS_001; WH_001; EU_001; TRD_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1794,13 +1786,13 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1815,16 +1807,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; CASE_008</t>
+          <t>CSIS_001; CASE_008; EU_001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; TRD_003; CASE_008; CASE_003; TRD_001; CASE_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; CASE_008; CASE_003; EU_001; CASE_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1857,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1896,13 +1888,13 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1917,16 +1909,16 @@
         <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; MOFCOM_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001; MOFCOM_002; CASE_003; WTO_001; CASE_010; MOFCOM_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002; CASE_003; CASE_010; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1974,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; TRD_003; CSIS_001; CASE_008; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2008,13 +2000,13 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2029,16 +2021,16 @@
         <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; CSIS_001; WTO_001; UNCTAD_001</t>
+          <t>CASE_003; DOC_001; CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003; CASE_010; CSIS_001; WTO_001; WH_001; UNCTAD_001</t>
+          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002; DOC_001; CSIS_001; WH_001; WTO_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2071,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001; TRD_003; CASE_008; CASE_004; CASE_006; CASE_005</t>
+          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; CASE_008; CASE_004; CASE_006; EU_003</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; CASE_001; TRD_003; CASE_008; CASE_004; CASE_006; CASE_005</t>
+          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; CASE_008; CASE_004; CASE_006; EU_003</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2132,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_001; TRD_003; CASE_003; CSIS_001; CASE_002; TRD_002; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; CSIS_001; CASE_002; TRD_001; TRD_002; TRD_003; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2382,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_006; CASE_005</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2410,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; KPMG_001</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2438,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2466,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_008; CASE_007</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_008; CASE_007; CASE_004</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2494,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009</t>
+          <t>BIS_002; BIS_001; CASE_009</t>
         </is>
       </c>
     </row>
@@ -2526,11 +2518,11 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MOFCOM_002; CASE_002; TRD_001</t>
+          <t>MOFCOM_002; MOFCOM_001; IRS_001; EU_003; UST_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2554,11 +2546,11 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MOFCOM_002; CASE_002</t>
+          <t>MOFCOM_002; IRS_001; EU_003; UST_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2578,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; MOFCOM_002; CASE_002; CASE_003</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; IRS_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2606,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002</t>
+          <t>CASE_009; BIS_002; BIS_001</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2670,7 +2662,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001; CASE_002</t>
+          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2718,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001; ITA_001</t>
         </is>
       </c>
     </row>
@@ -2750,11 +2742,11 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2778,11 +2770,11 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_002; TRD_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2802,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2834,11 +2826,11 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASE_010; WH_001; CASE_002; CASE_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2862,11 +2854,11 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2886,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_003; WH_002; WH_001</t>
+          <t>CASE_010; WH_001; WH_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2914,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; WH_001; CASE_001; CASE_009; MOFCOM_002</t>
+          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001; CASE_009</t>
         </is>
       </c>
     </row>
@@ -2946,11 +2938,11 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CNGOV_001; TRD_001; TRD_003; KPMG_001; CASE_002</t>
+          <t>CNGOV_001; IRS_001; EU_003; UST_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3006,7 +2998,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FR_001; WH_002</t>
+          <t>FR_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3054,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_002; CASE_007</t>
+          <t>TRD_001; TRD_003; CASE_002; IRS_001; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3082,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_002; IRS_001</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3110,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; TRD_002; CASE_003; CASE_002; CASE_010</t>
+          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3138,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; TRD_002; CASE_002; CASE_010</t>
+          <t>TRD_001; TRD_002; TRD_003; WH_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3166,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_002; CASE_003; CASE_002; CASE_010</t>
+          <t>TRD_001; CASE_003; TRD_002; WH_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3194,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; TRD_002; CASE_003; CASE_002; CASE_010</t>
+          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3222,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; TRD_001; CASE_002</t>
+          <t>TRD_003; CASE_002; CASE_008; UST_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3278,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; TRD_001; KPMG_001; CASE_007</t>
+          <t>CASE_002; TRD_003; CASE_008; TRD_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3306,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; TRD_001; TRD_002; CASE_003</t>
+          <t>TRD_003; CASE_010; WH_002; TRD_001; TRD_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3334,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; TRD_001; TRD_002</t>
+          <t>TRD_003; CASE_010; WH_002; TRD_001; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3362,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; WH_001</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3446,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CASE_010; WH_001; CASE_002; CASE_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3474,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3506,11 +3498,11 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CASE_002; MOFCOM_002</t>
+          <t>EU_001; IRS_001; UST_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3530,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; CASE_003; CASE_010; CASE_001</t>
+          <t>BIS_001; BIS_002; CASE_009; IRS_001; CASE_003; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3558,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003</t>
+          <t>CASE_002; DOC_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3586,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; TRD_002</t>
+          <t>CASE_002; DOC_001; CASE_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3614,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_010; TRD_001; TRD_002; TRD_003</t>
+          <t>CASE_002; DOC_001; CASE_010; WH_002; TRD_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3642,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_001; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3670,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; TRD_001; TRD_002</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; TRD_002</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3726,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASE_010; WH_001; CASE_002; CASE_003; TRD_001; CASE_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; CASE_001</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3754,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009</t>
+          <t>BIS_002; CASE_009; BIS_001</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3782,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3810,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; CASE_001; FR_001; MOFCOM_002</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3838,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_008</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_008; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3870,11 +3862,11 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; TRD_001</t>
+          <t>CASE_002; TRD_003; CASE_008; CASE_007</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3894,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; TRD_003; WH_001</t>
+          <t>CASE_010; WH_002; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3922,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_001; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3950,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002</t>
+          <t>TRD_003; CASE_002; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3978,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; WH_001</t>
+          <t>TRD_003; CASE_010; WH_002; WH_001</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4006,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_001; TRD_003; CASE_003; CASE_002; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_003; CASE_002; TRD_001; TRD_002</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4034,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_001; TRD_003; CASE_002; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4090,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CASE_010; WH_001; TRD_001; CASE_003; CASE_002; TRD_002</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; CASE_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4138,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.885</v>
+        <v>0.921</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -4176,7 +4168,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.771</v>
+        <v>0.842</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -4236,7 +4228,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/entity_accuracy.xlsx
+++ b/data/evaluation/entity_accuracy.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entity Detail'!$A$1:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entity Detail'!$A$1:$F$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -575,16 +575,16 @@
         <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_001; TSLA_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; TRD_003; CNGOV_001; EU_003</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; WB_001; TRD_003; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; TRD_001; CASE_001; CASE_008; CASE_004; CASE_005</t>
+          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; TRD_001; WB_001; CASE_001; CASE_008; CASE_004</t>
         </is>
       </c>
     </row>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -683,16 +683,12 @@
         <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>CASE_010</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; KPMG_001; CNGOV_001; EU_003; CASE_010</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; SNE_001; TSLA_001; KPMG_001; ALB_001</t>
         </is>
       </c>
     </row>
@@ -733,12 +729,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_001; CASE_002; TRD_003; CNGOV_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; WTO_004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_001; CASE_002; TRD_003; CNGOV_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; WTO_004</t>
         </is>
       </c>
     </row>
@@ -789,12 +785,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_001; EU_003; MOFCOM_002</t>
+          <t>DHS_001; CASE_010; CASE_001; EU_003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; CASE_001; CASE_008; CASE_007; EU_003; MOFCOM_002; CASE_004</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_010; CASE_001; CASE_008; CASE_007; EU_003; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -846,7 +842,7 @@
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; IRS_001; EU_003; CASE_003; UST_001; CASE_002</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -872,13 +868,13 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -893,16 +889,12 @@
         <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; CASE_002; CSIS_001; CASE_003; IRS_001; UST_001</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001; FR_001; XPEV_001; NIO_001; CASE_002; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -928,13 +920,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -949,16 +941,16 @@
         <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; EU_003</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001; ITA_001; CSIS_001; CASE_010; UST_001; EU_003</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001; ITA_001; FR_001; XPEV_001; DHS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -984,13 +976,13 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1005,16 +997,12 @@
         <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; TRD_001; TRD_003; CASE_007; TRD_002</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; USMCA_001; DHS_001; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1053,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; EU_003</t>
+          <t>EU_003; CASE_008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001; TRD_003; CASE_009; CASE_008; MOFCOM_002; EU_003</t>
+          <t>CASE_002; CASE_010; DHS_001; WH_001; WH_002; TRD_003; CASE_001; CASE_009; EU_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -1096,13 +1084,13 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1117,16 +1105,16 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; CASE_001; MCK_001; CSIS_001</t>
+          <t>IMF_001; UNCTAD_001; CASE_001; DHS_001; MCK_001; UST_001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001; IRS_001; CSIS_001; EU_003; UST_001; TRD_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001; SNE_001; IRS_001; MCK_001; EU_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1155,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; CASE_005</t>
+          <t>WTO_002; WEF_001; UNCTAD_001; CNGOV_001; WTO_004; TRD_003; DHS_001; EU_003; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; CASE_005</t>
+          <t>WTO_002; WEF_001; UNCTAD_001; CNGOV_001; WTO_004; TRD_003; DHS_001; EU_003; CASE_007; CASE_008</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1201,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; WTO_002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; WTO_002</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1262,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; MOFCOM_002; CASE_003; IRS_001; CASE_002</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; NIO_001; FR_001; XPEV_001; MOFCOM_001; MOFCOM_002; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1314,7 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; CASE_002; UST_001; MOFCOM_002; CASE_003; IRS_001</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; NIO_001; XPEV_001; UST_001; DHS_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -1352,13 +1340,13 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1373,16 +1361,12 @@
         <v>6</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002; CASE_002; CASE_010; IRS_001; CSIS_001; CASE_007</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; DHS_001; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1408,13 +1392,13 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1429,16 +1413,16 @@
         <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; WTO_001</t>
+          <t>WTO_001; DHS_001; UST_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; CSIS_001; WH_001; WTO_001; CASE_002; CASE_008; UST_001; TRD_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WTO_001; USMCA_001; DHS_001; WH_001; UST_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -1464,13 +1448,13 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1485,16 +1469,16 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; TRD_002</t>
+          <t>DHS_001; CASE_001; TSLA_001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; CASE_001; TRD_001; IRS_001; EU_003; TRD_002; MOFCOM_002; CASE_007</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; TRD_001; IRS_001; CASE_001; EU_003; TSLA_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1519,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004; CASE_007; CASE_006; CASE_005; CNGOV_001; EU_004</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; CASE_004; TSLA_001; DHS_001; CASE_007; CASE_006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; CASE_008; CASE_003; CASE_004; CASE_007; CASE_006; CASE_005; CNGOV_001; EU_004</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; CASE_004; TSLA_001; DHS_001; CASE_007; CASE_006</t>
         </is>
       </c>
     </row>
@@ -1566,13 +1550,13 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1587,16 +1571,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; WTO_001</t>
+          <t>WTO_001; DHS_001; IEA_001</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WH_001; CSIS_001; TRD_001; WTO_001; TRD_002; CASE_003; CASE_002</t>
+          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001; USMCA_001; WH_001; CASE_010; DHS_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1606,13 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1643,16 +1627,12 @@
         <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; CASE_003; TRD_003; TRD_001; UST_001; TRD_002</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; TRD_003; DHS_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1678,13 +1658,13 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1699,12 +1679,16 @@
         <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001; CASE_003; CASE_010; UST_001; CASE_001; EU_003</t>
+          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001; XPEV_001; NIO_001; IRS_001; UST_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1714,13 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1751,16 +1735,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; EU_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; CSIS_001; WH_001; EU_001; TRD_002; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001; CSIS_001; WH_001; EU_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1786,13 +1770,13 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1807,16 +1791,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>CSIS_001; CASE_008; EU_001</t>
+          <t>CASE_008; EU_001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; CASE_008; CASE_003; EU_001; CASE_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; CASE_008; EU_001; USMCA_001; CASE_003; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1841,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_001</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1888,13 +1872,13 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1909,16 +1893,12 @@
         <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>EU_003</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002; CASE_003; CASE_010; IRS_001; EU_003</t>
+          <t>BIS_002; CASE_009; BIS_001; CASE_001; FR_001; NIO_001; DHS_001; XPEV_001; MOFCOM_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -1944,13 +1924,13 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1965,16 +1945,12 @@
         <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; TRD_003; CSIS_001; CASE_008; CASE_007</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; USMCA_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2001,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; DOC_001; CSIS_001; WTO_001</t>
+          <t>CASE_003; DOC_001; WTO_001; DHS_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002; DOC_001; CSIS_001; WH_001; WTO_001; CASE_008</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2047,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; CASE_008; CASE_004; CASE_006; EU_003</t>
+          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; ALB_001; DHS_001; CASE_008</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; CASE_008; CASE_004; CASE_006; EU_003</t>
+          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; ALB_001; DHS_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2102,13 +2078,13 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2123,16 +2099,550 @@
         <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001; TRD_002; TRD_003; USMCA_001; CASE_007</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>China; EV Battery; Tariff</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001; IRS_001; TRD_001; WTO_003; CASE_002; EU_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Tariff; United States</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>CASE_010; WH_002; WH_001; CASE_003; CSIS_001; CASE_002; TRD_001; TRD_002; TRD_003; CASE_007</t>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_001</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001; MOFCOM_001; BIS_002; CASE_009; BIS_001; LI_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001; DHS_001; SNE_001; WH_002; TRD_001; EU_003; MOFCOM_002; WTO_002; IMF_001; IRS_001</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>ALB_001; DHS_001; SNE_001; WH_002; TRD_001; EU_003; MOFCOM_002; WTO_002; IMF_001; IRS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>China; EV Battery; Mexico; Tariff; Transshipment</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001; EU_003; UST_001; CASE_002; WTO_003; EU_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>India; Tariff</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; WTO_004; EU_002; MOFCOM_002; CNGOV_001</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004; CASE_001; EU_003; EU_002; MOFCOM_002; CNGOV_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>EV Battery; Indonesia</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; WTO_002; EU_003; MOFCOM_002; TSLA_001; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>China; Indonesia; Mexico; Vietnam</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; CASE_001</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_002; TRD_001; DHS_001; EU_003; CASE_003; SNE_001; CASE_010; IRS_001; CASE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>EV Battery; United States</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>CASE_008</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002; CASE_002; BIS_001; CASE_008; USMCA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>China; EV Battery</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>China; Indonesia; Mexico; Transshipment</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; EU_001</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001; IRS_001; WTO_004; CASE_002; DHS_001; EU_001; EU_002; EU_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2242,7 +2752,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_006; TRD_001; TRD_003</t>
+          <t>CASE_005; CASE_004; CASE_006; TRD_001; WB_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2780,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_002; TRD_003; TRD_001; CASE_008; CASE_004</t>
+          <t>CASE_007; CASE_002; TRD_003; TRD_001; WB_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2864,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; CASE_002; TRD_001; CASE_001</t>
+          <t>CASE_010; CASE_003; CASE_002; TRD_001; WB_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2892,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_006; CASE_005</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2920,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; KPMG_001</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; SNE_001</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2948,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASE_001; EU_003</t>
+          <t>CASE_001; TSLA_001; ALB_001</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2976,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_008; CASE_007; CASE_004</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_008; CASE_007; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -2522,7 +3032,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MOFCOM_002; MOFCOM_001; IRS_001; EU_003; UST_001; CASE_002</t>
+          <t>MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -2550,7 +3060,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MOFCOM_002; IRS_001; EU_003; UST_001; CASE_002</t>
+          <t>MOFCOM_002; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -2578,7 +3088,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; IRS_001; CASE_003</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; NIO_001; XPEV_001</t>
         </is>
       </c>
     </row>
@@ -2606,7 +3116,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_002; BIS_001</t>
+          <t>CASE_009; BIS_001; BIS_002</t>
         </is>
       </c>
     </row>
@@ -2630,11 +3140,11 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BIS_001; ITA_001</t>
+          <t>BIS_001; ITA_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -2662,7 +3172,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; CASE_002</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -2718,7 +3228,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; FR_001; ITA_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001; ITA_001</t>
         </is>
       </c>
     </row>
@@ -2746,7 +3256,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; TRD_003</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2774,7 +3284,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_003; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2802,7 +3312,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; USMCA_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2830,7 +3340,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; TRD_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3368,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_001; TRD_003</t>
+          <t>CASE_010; WH_002; CASE_002; CASE_003; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2914,7 +3424,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; WH_001; WH_002; CASE_001; CASE_009</t>
+          <t>CASE_002; CASE_010; DHS_001; WH_001; WH_002; CASE_001</t>
         </is>
       </c>
     </row>
@@ -2942,7 +3452,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CNGOV_001; IRS_001; EU_003; UST_001; TRD_001</t>
+          <t>CNGOV_001; SNE_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -2970,7 +3480,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_002</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; NIO_001; FR_001</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3536,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; CASE_002</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3564,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_002; IRS_001; CASE_007</t>
+          <t>TRD_001; TRD_003; CASE_002; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3078,11 +3588,11 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CASE_002; IRS_001</t>
+          <t>DHS_001; CASE_002; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3620,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002; CASE_002</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3648,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_002; TRD_003; WH_002; CASE_002; CASE_010</t>
+          <t>TRD_001; TRD_003; TRD_002; WH_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3676,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_002; WH_002; CASE_002; CASE_010</t>
+          <t>TRD_001; CASE_003; TRD_002; DHS_001; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3704,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_002; TRD_003; WH_002; CASE_002</t>
+          <t>TRD_001; TRD_003; CASE_003; TRD_002; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3732,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; UST_001; TRD_001</t>
+          <t>TRD_003; USMCA_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3760,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WH_001</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; USMCA_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3816,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; TRD_001; TRD_002; CASE_003</t>
+          <t>TRD_003; WH_002; TRD_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3844,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; TRD_001; TRD_002; CASE_002</t>
+          <t>TRD_003; WH_002; TRD_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3872,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WH_001</t>
+          <t>TRD_003; WH_002; CSIS_001; USMCA_001; WH_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3386,11 +3896,11 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; TRD_002</t>
+          <t>CSIS_001; CASE_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3928,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3956,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; TRD_001</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3502,7 +4012,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>EU_001; IRS_001; UST_001; EU_003</t>
+          <t>DHS_001; EU_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -3530,7 +4040,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; IRS_001; CASE_003; CASE_010</t>
+          <t>BIS_001; BIS_002; CASE_009; DHS_001; XPEV_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -3586,7 +4096,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; TRD_002</t>
+          <t>CASE_002; DOC_001; CASE_003; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -3614,7 +4124,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_010; WH_002; TRD_002; TRD_001</t>
+          <t>CASE_002; DOC_001; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3642,7 +4152,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3670,7 +4180,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; TRD_002</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3698,7 +4208,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3726,7 +4236,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CASE_003; CASE_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3810,7 +4320,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002</t>
+          <t>BIS_002; CASE_009; BIS_001; CASE_001; FR_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -3838,7 +4348,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_008; CASE_007</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3866,7 +4376,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; CASE_007</t>
+          <t>CASE_002; TRD_003; CASE_008; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3894,7 +4404,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>WH_002; TRD_003; WH_001; CSIS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3922,7 +4432,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -3950,7 +4460,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008</t>
+          <t>TRD_003; CASE_002; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -3978,7 +4488,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WH_001</t>
+          <t>TRD_003; WH_002; CASE_010; CSIS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4516,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_003; CASE_002; TRD_001; TRD_002</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4572,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; TRD_003; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4600,740 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_003; CASE_002; TRD_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>EU_003; SNE_001; IRS_001; TRD_001; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>TSLA_001; EU_003; DHS_001; SNE_001; IRS_001; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TSLA_001; EU_003; UST_001; WTO_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FR_001; LI_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001; BIS_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>USMCA_001; SNE_001; IRS_001; EU_003; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>USMCA_001; DHS_001; SNE_001; IRS_001; EU_003; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>USMCA_001; EU_003; UST_001; WTO_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Transshipment</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>USMCA_001; CSIS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003; CASE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003; CASE_001; EU_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; WTO_002; EU_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_002; TRD_001; EU_003; SNE_001; IRS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_002; TRD_001; CASE_003; CASE_010</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DHS_001; IRS_001; TSLA_001; CASE_002; BIS_001; USMCA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SNE_001; EU_003; IRS_001; CASE_002; MOFCOM_002; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001; IRS_001; CASE_002; EU_002; EU_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>WB_001; WTO_004</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>USMCA_001; WB_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Transshipment</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F69"/>
+  <autoFilter ref="A1:F95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4138,11 +5376,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.93</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>mean over 24 entity-bearing questions</t>
+          <t>mean over 33 entity-bearing questions</t>
         </is>
       </c>
     </row>
@@ -4168,7 +5406,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.842</v>
+        <v>0.861</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -4183,11 +5421,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>of 30 (entity-free questions excluded)</t>
+          <t>of 40 (entity-free questions excluded)</t>
         </is>
       </c>
     </row>
@@ -4198,11 +5436,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Q004; Q012; Q013; Q019; Q025; Q029</t>
+          <t>Q004; Q012; Q013; Q019; Q025; Q029; Q033</t>
         </is>
       </c>
     </row>
@@ -4213,11 +5451,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>of 24</t>
+          <t>of 33</t>
         </is>
       </c>
     </row>
@@ -4228,11 +5466,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>of 24</t>
+          <t>of 33</t>
         </is>
       </c>
     </row>
@@ -4243,7 +5481,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -4295,10 +5533,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -4308,10 +5546,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -4321,10 +5559,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">

--- a/data/evaluation/entity_accuracy.xlsx
+++ b/data/evaluation/entity_accuracy.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entity Detail'!$A$1:$F$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Entity Detail'!$A$1:$F$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -842,7 +842,7 @@
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
+          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; DHS_001; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
+          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001; XPEV_001; NIO_001; IRS_001; UST_001; EU_003</t>
+          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001; XPEV_001; NIO_001; IRS_001; MOFCOM_002; UST_001</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001; IRS_001; TRD_001; WTO_003; CASE_002; EU_001</t>
+          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001; TRD_001; IRS_001; WTO_003; CASE_002; EU_001</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001; EU_003; UST_001; CASE_002; WTO_003; EU_001</t>
+          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001; EU_003; UST_001; TRD_001; CASE_002; WTO_003</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; WTO_002; EU_003; MOFCOM_002; TSLA_001; EU_002</t>
+          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; WTO_002; EU_003; MOFCOM_002; TSLA_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2500,13 +2500,13 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2521,16 +2521,12 @@
         <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>CASE_008</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002; CASE_002; BIS_001; CASE_008; USMCA_001</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; MOFCOM_002; EU_002; CASE_002; BIS_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2582,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002; EU_002</t>
+          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2643,6 +2639,170 @@
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>USMCA_001; WB_001; IRS_001; WTO_004; CASE_002; DHS_001; EU_001; EU_002; EU_003; TRD_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001; UST_001</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001; IEA_001; UST_001; TRD_001; MOFCOM_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>AD/CVD; China; EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; SNE_001; IRS_001; IEA_001; EU_001; UST_001; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>China; EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004; DHS_001; EU_001; EU_003; CASE_002; IRS_001; SNE_001; TRD_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3028,7 +3188,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3056,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3088,7 +3248,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; NIO_001; XPEV_001</t>
+          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; NIO_001; XPEV_001</t>
         </is>
       </c>
     </row>
@@ -3588,11 +3748,11 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_002; IRS_001; SNE_001</t>
+          <t>TRD_001; DHS_001; CASE_002; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3836,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_002; DHS_001; WH_002; CASE_002</t>
+          <t>TRD_001; CASE_003; DHS_001; TRD_002; WH_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4172,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DHS_001; EU_001; IRS_001; EU_003</t>
+          <t>DHS_001; EU_001; IRS_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4788,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>EU_003; SNE_001; IRS_001; TRD_001; CASE_002</t>
+          <t>EU_003; SNE_001; TRD_001; IRS_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4816,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; DHS_001; SNE_001; IRS_001; CASE_002</t>
+          <t>TSLA_001; EU_003; DHS_001; SNE_001; TRD_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4928,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>USMCA_001; SNE_001; IRS_001; EU_003; CASE_002</t>
+          <t>USMCA_001; SNE_001; IRS_001; EU_003; TRD_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4956,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>USMCA_001; DHS_001; SNE_001; IRS_001; EU_003; CASE_002</t>
+          <t>USMCA_001; DHS_001; SNE_001; IRS_001; EU_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5292,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5320,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; TSLA_001; CASE_002; BIS_001; USMCA_001</t>
+          <t>DHS_001; IRS_001; TSLA_001; MOFCOM_002; CASE_002; BIS_001</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5348,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SNE_001; EU_003; IRS_001; CASE_002; MOFCOM_002; EU_002</t>
+          <t>SNE_001; TRD_001; EU_003; IRS_001; CASE_002; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5376,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001</t>
+          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001; EU_001</t>
         </is>
       </c>
     </row>
@@ -5332,8 +5492,260 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>EU_001; EU_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>EU_001; DHS_001; EU_003; SNE_001; IRS_001; IEA_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AD/CVD</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; TRD_001; SNE_001; IRS_001; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>EU_003; EU_001; EU_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; SNE_001; IRS_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>EU_002; EU_003; CASE_002; IRS_001; SNE_001; TRD_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004; EU_001; EU_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EV Battery</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>EU_002; DHS_001; EU_001; EU_003; CASE_002; IRS_001</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F95"/>
+  <autoFilter ref="A1:F104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5376,11 +5788,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>mean over 33 entity-bearing questions</t>
+          <t>mean over 36 entity-bearing questions</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5818,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -5421,11 +5833,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>of 40 (entity-free questions excluded)</t>
+          <t>of 43 (entity-free questions excluded)</t>
         </is>
       </c>
     </row>
@@ -5451,11 +5863,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>of 33</t>
+          <t>of 36</t>
         </is>
       </c>
     </row>
@@ -5466,11 +5878,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>of 33</t>
+          <t>of 36</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5893,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -5533,10 +5945,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -5546,10 +5958,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -5559,10 +5971,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">

--- a/data/evaluation/entity_accuracy.xlsx
+++ b/data/evaluation/entity_accuracy.xlsx
@@ -636,7 +636,7 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; TRD_001; WB_001; CASE_001; CASE_008; CASE_004</t>
+          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; CASE_001; CASE_008; CASE_004</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; WTO_004</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; WTO_004; TRD_003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; TRD_003; WTO_004</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; WTO_004; TRD_003</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001; ITA_001; FR_001; XPEV_001; DHS_001; UST_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; ITA_001; NIO_001; FR_001; XPEV_001; DHS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; WTO_002</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; WTO_002</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
+          <t>TRD_001; CASE_003; TRD_003; DHS_001; WH_002; TRD_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; TRD_001; IRS_001; CASE_001; EU_003; TSLA_001; SNE_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; IRS_001; TRD_001; CASE_001; TSLA_001; EU_003; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; CASE_004; TSLA_001; DHS_001; CASE_007; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; TSLA_001; DHS_001; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; CASE_004; TSLA_001; DHS_001; CASE_007; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; TSLA_001; DHS_001; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001; USMCA_001; WH_001; CASE_010; DHS_001; IEA_001</t>
+          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001; CASE_010; USMCA_001; WH_001; DHS_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; TRD_003; DHS_001; TRD_001</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; DHS_001; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; USMCA_001; DHS_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001; CSIS_001; TRD_003; CASE_008; USMCA_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001; MOFCOM_001; BIS_002; CASE_009; BIS_001; LI_001</t>
+          <t>NIO_001; XPEV_001; MOFCOM_002; FR_001; ITA_001; MOFCOM_001; BIS_002; BIS_001; CASE_009; LI_001</t>
         </is>
       </c>
     </row>
@@ -2336,13 +2336,13 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2357,16 +2357,16 @@
         <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; WTO_004; EU_002; MOFCOM_002; CNGOV_001</t>
+          <t>DHS_001; IRS_001; WTO_004; ITA_001; EU_002</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004; CASE_001; EU_003; EU_002; MOFCOM_002; CNGOV_001</t>
+          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004; CASE_001; ITA_001; EU_003; FR_001; EU_002</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001; IEA_001; UST_001; TRD_001; MOFCOM_002</t>
+          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001; IEA_001; TRD_001; UST_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_002; TRD_003; TRD_001; WB_001; CASE_008</t>
+          <t>CASE_007; CASE_002; TRD_003; WB_001; TRD_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; TRD_001</t>
+          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; WB_001</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; CASE_002; TRD_001; WB_001; CASE_001</t>
+          <t>CASE_010; CASE_003; CASE_002; WB_001; TRD_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; NIO_001; ITA_001</t>
+          <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; ITA_001; NIO_001</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; WH_002; CASE_002</t>
+          <t>TRD_001; CASE_003; TRD_003; WH_002; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; TRD_002; WH_002; CASE_002; CASE_010</t>
+          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; DHS_001; TRD_002; WH_002; CASE_002</t>
+          <t>TRD_001; CASE_003; DHS_001; WH_002; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; TRD_002; WH_002; CASE_002</t>
+          <t>TRD_001; CASE_003; TRD_003; WH_002; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; TRD_001; IRS_001; EU_003</t>
+          <t>CASE_002; TRD_003; CASE_008; IRS_001; TRD_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; USMCA_001; WH_001; CASE_010</t>
+          <t>TRD_003; WH_002; CSIS_001; CASE_010; USMCA_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>WH_002; TRD_003; WH_001; CSIS_001; USMCA_001</t>
+          <t>WH_002; WH_001; CSIS_001; TRD_003; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; FR_001; MOFCOM_002; ITA_001; BIS_002</t>
+          <t>NIO_001; XPEV_001; MOFCOM_002; FR_001; ITA_001; BIS_002</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; CASE_001; EU_003</t>
+          <t>WTO_002; WTO_003; CASE_001; EU_003; FR_001</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SNE_001; TRD_001; DHS_001; EU_003; IRS_001; EU_001</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; IRS_001; EU_001</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.867</v>
+        <v>0.869</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/entity_accuracy.xlsx
+++ b/data/evaluation/entity_accuracy.xlsx
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -575,16 +575,16 @@
         <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; TSLA_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; WB_001; TRD_003; TSLA_001</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; MOFCOM_006; MOFCOM_005; TRD_001; WB_001</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; CASE_001; CASE_008; CASE_004</t>
+          <t>CASE_007; CASE_010; CASE_002; CASE_003; MOFCOM_004; TRD_003; WB_001; TRD_001; CASE_008; CASE_001</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; SNE_001; TSLA_001; KPMG_001; ALB_001</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; SNE_001; TSLA_001; ALB_001; KPMG_001</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; WTO_004; TRD_003</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; MOFCOM_004; CASE_010; MOFCOM_006; MOFCOM_003; CASE_002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; CASE_010; CASE_002; CASE_001; WTO_004; TRD_003</t>
+          <t>CASE_008; CASE_007; CASE_004; CASE_005; CASE_006; MOFCOM_004; CASE_010; MOFCOM_006; MOFCOM_003; CASE_002</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_010; CASE_001; EU_003</t>
+          <t>DHS_001; CASE_001; CASE_010; EU_003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_010; CASE_001; CASE_008; CASE_007; EU_003; TSLA_001</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_001; CASE_010; EU_003; CASE_007; CASE_008; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
+          <t>MOFCOM_002; BIS_002; BIS_001; CASE_009; MOFCOM_001; NIO_001; XPEV_001; DHS_001; IRS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -868,13 +868,13 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -889,12 +889,16 @@
         <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001; FR_001; XPEV_001; NIO_001; CASE_002; USMCA_001</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001; XPEV_001; FR_001; NIO_001; USMCA_001; CSIS_001</t>
         </is>
       </c>
     </row>
@@ -920,13 +924,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -941,13 +945,9 @@
         <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>BIS_002; CASE_009; BIS_001; MOFCOM_002; ITA_001; NIO_001; FR_001; XPEV_001; DHS_001; UST_001</t>
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -997,12 +997,16 @@
         <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; USMCA_001; DHS_001; TRD_003; TRD_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; USMCA_001; CASE_003; DHS_001; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1028,13 +1032,13 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>0.9</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1049,16 +1053,16 @@
         <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>EU_003; CASE_008</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; DHS_001; WH_001; WH_002; TRD_003; CASE_001; CASE_009; EU_003; CASE_008</t>
+          <t>CASE_002; CASE_010; DHS_001; WH_001; WH_002; TRD_003; MOFCOM_006; EU_003; CASE_001; CASE_009</t>
         </is>
       </c>
     </row>
@@ -1084,13 +1088,13 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1105,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; CASE_001; DHS_001; MCK_001; UST_001</t>
+          <t>MOFCOM_006; IMF_001; UNCTAD_001; CASE_001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001; SNE_001; IRS_001; MCK_001; EU_003; UST_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_006; CNGOV_001; MOFCOM_004; IMF_001; UNCTAD_001; CASE_001; SNE_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1159,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WTO_002; WEF_001; UNCTAD_001; CNGOV_001; WTO_004; TRD_003; DHS_001; EU_003; CASE_007; CASE_008</t>
+          <t>WEF_001; WTO_002; MOFCOM_003; UNCTAD_001; MOFCOM_006; MOFCOM_004; MOFCOM_005; WTO_004; CNGOV_001; TRD_003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>WTO_002; WEF_001; UNCTAD_001; CNGOV_001; WTO_004; TRD_003; DHS_001; EU_003; CASE_007; CASE_008</t>
+          <t>WEF_001; WTO_002; MOFCOM_003; UNCTAD_001; MOFCOM_006; MOFCOM_004; MOFCOM_005; WTO_004; CNGOV_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1205,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; CNGOV_001; EU_004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; CNGOV_001; EU_004</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1318,7 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; NIO_001; XPEV_001; UST_001; DHS_001; CASE_002</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; NIO_001; BIS_001; XPEV_001; UST_001; DHS_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1370,7 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; TRD_003; DHS_001; WH_002; TRD_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
+          <t>TRD_001; DHS_001; CASE_003; TRD_003; WH_002; TRD_002; CASE_002; IRS_001; SNE_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1421,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; DHS_001; UST_001</t>
+          <t>CSIS_001; WTO_001; DHS_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; CSIS_001; WTO_001; USMCA_001; DHS_001; WH_001; UST_001; CASE_002</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WTO_001; USMCA_001; DHS_001; WH_001; CASE_002; UST_001</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1477,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_001; TSLA_001</t>
+          <t>DHS_001; TSLA_001; CASE_001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; IRS_001; TRD_001; CASE_001; TSLA_001; EU_003; SNE_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; MOFCOM_003; TSLA_001; IRS_001; CASE_001; EU_003; SNE_001</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1523,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; TSLA_001; DHS_001; CASE_007; CASE_004; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; TSLA_001; CASE_003; CASE_007; CASE_004; DHS_001; ALB_001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_003; CASE_008; TSLA_001; DHS_001; CASE_007; CASE_004; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; TSLA_001; CASE_003; CASE_007; CASE_004; DHS_001; ALB_001</t>
         </is>
       </c>
     </row>
@@ -1550,13 +1554,13 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1571,16 +1575,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>WTO_001; DHS_001; IEA_001</t>
+          <t>CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; TRD_001; WTO_001; CASE_010; USMCA_001; WH_001; DHS_001; IEA_001</t>
+          <t>TRD_003; WH_002; CSIS_001; WTO_001; TRD_001; MOFCOM_004; CASE_010; USMCA_001; WH_001; MOFCOM_006</t>
         </is>
       </c>
     </row>
@@ -1606,13 +1610,13 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1627,12 +1631,16 @@
         <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; DHS_001; TRD_003; TRD_001</t>
+          <t>CSIS_001; CASE_010; USMCA_001; WH_002; WH_001; CASE_002; DHS_001; CASE_003; TRD_003; TRD_001</t>
         </is>
       </c>
     </row>
@@ -1658,13 +1666,13 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1679,16 +1687,12 @@
         <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; DHS_001; EU_001; XPEV_001; NIO_001; IRS_001; MOFCOM_002; UST_001</t>
+          <t>BIS_001; CASE_009; DHS_001; BIS_002; EU_001; NIO_001; XPEV_001; MOFCOM_002; IRS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -1714,13 +1718,13 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1735,16 +1739,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>CSIS_001; EU_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001; CSIS_001; WH_001; EU_001; DHS_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; USMCA_001; CASE_010; CSIS_001; WH_001; EU_001; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1770,13 +1774,13 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1791,16 +1795,16 @@
         <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; EU_001</t>
+          <t>CSIS_001; EU_001; CASE_008</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; CASE_008; EU_001; USMCA_001; CASE_003; DHS_001</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; EU_001; USMCA_001; CASE_008; CASE_003; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1845,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MOFCOM_004; MOFCOM_003; WTO_002; MCK_001; MOFCOM_006; MOFCOM_005; WTO_003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MOFCOM_004; MOFCOM_003; WTO_002; MCK_001; MOFCOM_006; MOFCOM_005; WTO_003</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1902,7 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; CASE_001; FR_001; NIO_001; DHS_001; XPEV_001; MOFCOM_002; CASE_003</t>
+          <t>BIS_002; CASE_009; BIS_001; NIO_001; FR_001; CASE_001; DHS_001; MOFCOM_002; XPEV_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1928,13 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1945,12 +1949,16 @@
         <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001; CSIS_001; TRD_003; CASE_008; USMCA_001; DHS_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001; CSIS_001; CASE_008; USMCA_001; TRD_003; DHS_001</t>
         </is>
       </c>
     </row>
@@ -1976,13 +1984,13 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -1997,16 +2005,16 @@
         <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; DOC_001; WTO_001; DHS_001</t>
+          <t>DOC_001; CASE_003; CSIS_001; WTO_001; DHS_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
+          <t>TRD_003; CASE_002; WH_002; DOC_001; CASE_010; CASE_003; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2055,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; ALB_001; DHS_001; CASE_008</t>
+          <t>WTO_001; WTO_002; IMF_001; CNGOV_001; UNCTAD_001; MOFCOM_005; CASE_001; EU_004; MOFCOM_004; MOFCOM_003</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; CASE_001; ALB_001; DHS_001; CASE_008</t>
+          <t>WTO_001; WTO_002; IMF_001; CNGOV_001; UNCTAD_001; MOFCOM_005; CASE_001; EU_004; MOFCOM_004; MOFCOM_003</t>
         </is>
       </c>
     </row>
@@ -2078,13 +2086,13 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2099,12 +2107,16 @@
         <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001; TRD_002; TRD_003; USMCA_001; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; TRD_001; USMCA_001; TRD_003; TRD_002; CASE_007</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2142,13 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2151,12 +2163,16 @@
         <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001; TRD_001; IRS_001; WTO_003; CASE_002; EU_001</t>
+          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001; IRS_001; MOFCOM_006; TRD_001; EU_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2228,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; MOFCOM_002; FR_001; ITA_001; MOFCOM_001; BIS_002; BIS_001; CASE_009; LI_001</t>
+          <t>NIO_001; XPEV_001; MOFCOM_002; FR_001; ITA_001; BIS_002; MOFCOM_001; CASE_009; BIS_001; LI_001</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2269,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; SNE_001; WH_002; TRD_001; EU_003; MOFCOM_002; WTO_002; IMF_001; IRS_001</t>
+          <t>ALB_001; DHS_001; SNE_001; TRD_001; EU_003; WH_002; MOFCOM_005; MOFCOM_002; IRS_001; MOFCOM_006</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; SNE_001; WH_002; TRD_001; EU_003; MOFCOM_002; WTO_002; IMF_001; IRS_001</t>
+          <t>ALB_001; DHS_001; SNE_001; TRD_001; EU_003; WH_002; MOFCOM_005; MOFCOM_002; IRS_001; MOFCOM_006</t>
         </is>
       </c>
     </row>
@@ -2284,13 +2300,13 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2305,12 +2321,16 @@
         <v>5</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001; EU_003; UST_001; TRD_001; CASE_002; WTO_003</t>
+          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001; EU_003; UST_001; TRD_001; MOFCOM_006; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2381,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; WTO_004; ITA_001; EU_002</t>
+          <t>IRS_001; WTO_004; DHS_001; EU_002; ITA_001</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; DHS_001; IRS_001; WTO_004; CASE_001; ITA_001; EU_003; FR_001; EU_002</t>
+          <t>WTO_002; WTO_003; IRS_001; WTO_004; DHS_001; MOFCOM_005; EU_003; CASE_001; EU_002; ITA_001</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2438,7 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; WTO_002; EU_003; MOFCOM_002; TSLA_001; TRD_001</t>
+          <t>WTO_004; IRS_001; DHS_001; EU_001; MOFCOM_004; WTO_002; EU_003; SNE_001; TSLA_001; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2494,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_002; TRD_001; DHS_001; EU_003; CASE_003; SNE_001; CASE_010; IRS_001; CASE_001</t>
+          <t>WB_001; CASE_002; DHS_001; TRD_001; EU_003; SNE_001; CASE_003; IRS_001; CASE_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2546,7 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; MOFCOM_002; EU_002; CASE_002; BIS_001; TRD_001</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002; TSLA_001; EU_002; CASE_002; TRD_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -2552,13 +2572,13 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2573,16 +2593,12 @@
         <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; TRD_001; EU_003; IRS_001; EU_001; IEA_001; CASE_002; UST_001; MOFCOM_002</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; IRS_001; EU_001; IEA_001; UST_001; CASE_002; MOFCOM_002</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2654,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>USMCA_001; WB_001; IRS_001; WTO_004; CASE_002; DHS_001; EU_001; EU_002; EU_003; TRD_001</t>
+          <t>USMCA_001; WB_001; IRS_001; CASE_002; WTO_004; DHS_001; EU_001; TRD_001; EU_003; EU_002</t>
         </is>
       </c>
     </row>
@@ -2664,13 +2680,13 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2685,16 +2701,12 @@
         <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>CSIS_001; UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001; IEA_001; TRD_001; UST_001; MOFCOM_002</t>
+          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001; IEA_001; UST_001; TRD_001; ALB_001</t>
         </is>
       </c>
     </row>
@@ -2720,13 +2732,13 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -2741,13 +2753,9 @@
         <v>4</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>EU_003; CASE_002; DHS_001; TRD_001; SNE_001; IRS_001; IEA_001; EU_001; UST_001; EU_002</t>
@@ -2884,7 +2892,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_006; CASE_008; CASE_007; TRD_001</t>
+          <t>CASE_005; CASE_004; CASE_006; CASE_008; CASE_007; MOFCOM_005</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2920,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_006; TRD_001; WB_001; TRD_003</t>
+          <t>CASE_005; CASE_004; CASE_006; MOFCOM_006; TRD_001; WB_001</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2948,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_002; TRD_003; WB_001; TRD_001; CASE_008</t>
+          <t>CASE_007; CASE_002; MOFCOM_004; TRD_003; WB_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2976,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; CASE_003; CASE_002; TRD_003; WB_001</t>
+          <t>CASE_007; CASE_010; CASE_002; CASE_003; MOFCOM_004; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3004,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASE_010; TRD_003</t>
+          <t>CASE_010; MOFCOM_004; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3032,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; CASE_002; WB_001; TRD_001; CASE_001</t>
+          <t>CASE_010; CASE_002; CASE_003; MOFCOM_004; WB_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3144,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_008; CASE_007; TSLA_001</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_007; CASE_008; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3188,11 +3196,11 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; EU_003; IRS_001</t>
+          <t>MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; IRS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -3216,11 +3224,11 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MOFCOM_002; DHS_001; EU_003; IRS_001</t>
+          <t>MOFCOM_002; DHS_001; IRS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3256,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; NIO_001; XPEV_001</t>
+          <t>MOFCOM_002; BIS_002; BIS_001; CASE_009; NIO_001; XPEV_001</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3340,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001; FR_001</t>
+          <t>CASE_009; BIS_001; BIS_002; ITA_001; DHS_001; XPEV_001</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3480,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; USMCA_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; USMCA_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3508,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; USMCA_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3592,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_010; DHS_001; WH_001; WH_002; CASE_001</t>
+          <t>CASE_002; CASE_010; DHS_001; WH_001; WH_002; MOFCOM_006</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3620,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CNGOV_001; SNE_001; IRS_001; EU_003</t>
+          <t>MOFCOM_005; MOFCOM_003; CNGOV_001; MOFCOM_004; SNE_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3704,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; NIO_001</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; NIO_001; BIS_001</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3732,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_002; IRS_001; SNE_001</t>
+          <t>TRD_001; TRD_003; CASE_002; IRS_001; SNE_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3760,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TRD_001; DHS_001; CASE_002; IRS_001; SNE_001</t>
+          <t>TRD_001; DHS_001; CASE_002; IRS_001; SNE_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3816,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_002; CASE_010</t>
+          <t>TRD_001; TRD_003; WH_002; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3844,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TRD_001; CASE_003; DHS_001; WH_002; TRD_002; CASE_002</t>
+          <t>TRD_001; DHS_001; CASE_003; WH_002; TRD_002; CASE_002</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3900,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TRD_003; USMCA_001; CASE_002</t>
+          <t>TRD_003; USMCA_001; CASE_002; UST_001</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3928,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; CSIS_001; USMCA_001; WH_001</t>
+          <t>TRD_003; CASE_010; WH_002; USMCA_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3956,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; IRS_001; TRD_001; EU_003</t>
+          <t>CASE_002; TRD_003; CASE_008; MOFCOM_003; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3984,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; TRD_001; CASE_010</t>
+          <t>TRD_003; WH_002; TRD_001; MOFCOM_004; CASE_010</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4012,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; TRD_001; CASE_010</t>
+          <t>TRD_003; WH_002; TRD_001; CASE_010; MOFCOM_006</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4040,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CSIS_001; CASE_010; USMCA_001; WH_001</t>
+          <t>TRD_003; WH_002; MOFCOM_004; CASE_010; USMCA_001; WH_001</t>
         </is>
       </c>
     </row>
@@ -4056,11 +4064,11 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CSIS_001; CASE_002; CASE_003</t>
+          <t>CASE_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -4084,11 +4092,11 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; TRD_003</t>
+          <t>CASE_010; USMCA_001; WH_002; WH_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4112,11 +4120,11 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002</t>
+          <t>CASE_010; USMCA_001; WH_002; WH_001; CASE_002; DHS_001</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4168,11 +4176,11 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DHS_001; EU_001; IRS_001; MOFCOM_002</t>
+          <t>DHS_001; EU_001; MOFCOM_002; IRS_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4208,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; DHS_001; XPEV_001; NIO_001</t>
+          <t>BIS_001; CASE_009; DHS_001; BIS_002; NIO_001; XPEV_001</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4236,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003</t>
+          <t>DOC_001; CASE_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4264,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CSIS_001</t>
+          <t>DOC_001; CASE_002; CASE_003</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4292,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; WH_002; CASE_010</t>
+          <t>DOC_001; CASE_002; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4320,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; USMCA_001; CASE_010</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4348,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4376,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; USMCA_001</t>
+          <t>CASE_010; WH_002; WH_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4404,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; USMCA_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; USMCA_001; CASE_003</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4488,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; CASE_001; FR_001; NIO_001</t>
+          <t>BIS_002; CASE_009; BIS_001; NIO_001; FR_001; CASE_001</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4544,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; USMCA_001</t>
+          <t>CASE_002; CASE_008; USMCA_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4572,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>WH_002; WH_001; CSIS_001; TRD_003; USMCA_001</t>
+          <t>WH_002; WH_001; USMCA_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4600,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001; CSIS_001</t>
+          <t>CASE_002; DOC_001; CASE_003; WH_002; WH_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4656,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; CSIS_001; USMCA_001</t>
+          <t>TRD_003; WH_002; CASE_010; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4684,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_002; TRD_003</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4712,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_002; TRD_003</t>
+          <t>CASE_010; WH_002; CASE_002; TRD_001; TRD_003; TRD_002</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4740,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; TRD_003; USMCA_001</t>
+          <t>CASE_010; WH_002; WH_001; USMCA_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4768,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; TRD_001; USMCA_001</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4796,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>EU_003; SNE_001; TRD_001; IRS_001; CASE_002</t>
+          <t>EU_003; UST_001; SNE_001; IRS_001; TRD_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4824,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; DHS_001; SNE_001; TRD_001; IRS_001</t>
+          <t>TSLA_001; EU_003; UST_001; DHS_001; SNE_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4852,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; UST_001; WTO_003</t>
+          <t>TSLA_001; EU_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4936,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>USMCA_001; SNE_001; IRS_001; EU_003; TRD_001; CASE_002</t>
+          <t>USMCA_001; SNE_001; IRS_001; EU_003; UST_001; TRD_001</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4964,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>USMCA_001; DHS_001; SNE_001; IRS_001; EU_003; TRD_001</t>
+          <t>USMCA_001; DHS_001; CSIS_001; SNE_001; IRS_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5020,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>USMCA_001; EU_003; UST_001; WTO_003</t>
+          <t>USMCA_001; EU_003; UST_001</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5048,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>USMCA_001; CSIS_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5076,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; CASE_001</t>
+          <t>WTO_002; WTO_003; MOFCOM_005; CASE_001</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5104,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; CASE_001; EU_003; FR_001</t>
+          <t>WTO_002; WTO_003; EU_003; CASE_001</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5132,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; WTO_002; EU_003</t>
+          <t>IRS_001; DHS_001; EU_001; WTO_002; EU_003; SNE_001</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5160,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>WTO_004; MOFCOM_004</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5300,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; MOFCOM_002</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002; TSLA_001</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5328,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; TSLA_001; MOFCOM_002; CASE_002; BIS_001</t>
+          <t>DHS_001; IRS_001; MOFCOM_002; TSLA_001; CASE_002; TRD_001</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5356,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SNE_001; TRD_001; EU_003; IRS_001; CASE_002; MOFCOM_002</t>
+          <t>SNE_001; TRD_001; EU_003; IRS_001; IEA_001; UST_001</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5412,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>USMCA_001; WB_001; IRS_001; CASE_002; EU_002; EU_003</t>
+          <t>USMCA_001; WB_001; IRS_001; CASE_002; TRD_001; EU_003</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5552,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>EU_001; DHS_001; EU_003; SNE_001; IRS_001; IEA_001</t>
+          <t>EU_001; DHS_001; EU_003; CSIS_001; SNE_001; IRS_001</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5608,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>EU_003; CASE_002; TRD_001; SNE_001; IRS_001; EU_002</t>
+          <t>EU_003; CASE_002; TRD_001; SNE_001; IRS_001; IEA_001</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5796,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -5818,7 +5826,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.869</v>
+        <v>0.872</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -5878,7 +5886,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
